--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91308</v>
+        <v>91324</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91324</v>
+        <v>91336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91336</v>
+        <v>91358</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91358</v>
+        <v>91362</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91362</v>
+        <v>91368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91368</v>
+        <v>91375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91375</v>
+        <v>91380</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>16044867</v>
       </c>
       <c r="B16" t="n">
-        <v>91380</v>
+        <v>91408</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 44561-2021 artfynd.xlsx
+++ b/artfynd/A 44561-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
